--- a/aeromaps/utils/calibration_notebooks/fleet_calibrated_inputs_processed_here/other_parameters.xlsx
+++ b/aeromaps/utils/calibration_notebooks/fleet_calibrated_inputs_processed_here/other_parameters.xlsx
@@ -448,7 +448,7 @@
         <v>-0.01</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1337681796514948</v>
+        <v>0.1857285311230981</v>
       </c>
     </row>
   </sheetData>

--- a/aeromaps/utils/calibration_notebooks/fleet_calibrated_inputs_processed_here/other_parameters.xlsx
+++ b/aeromaps/utils/calibration_notebooks/fleet_calibrated_inputs_processed_here/other_parameters.xlsx
@@ -448,7 +448,7 @@
         <v>-0.01</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1857285311230981</v>
+        <v>0.1895986255746087</v>
       </c>
     </row>
   </sheetData>
